--- a/toolkit/value-study-logbook.xlsx
+++ b/toolkit/value-study-logbook.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Signed?</t>
+          <t>Signed (Y/N)</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="G39" s="11">
-        <f>COUNTIF(J8:J37,"Yes")</f>
+        <f>COUNTIF(J8:J37,"Y")</f>
         <v/>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       <formula1>"Team member,Assistant facilitator,Facilitator,Specialist,Sponsor"</formula1>
     </dataValidation>
     <dataValidation sqref="J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
+      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
